--- a/docs/The_Called_Scoreboard.xlsx
+++ b/docs/The_Called_Scoreboard.xlsx
@@ -23485,7 +23485,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="17" customHeight="1">
+    <row r="41" ht="43" customHeight="1">
       <c r="A41" s="94" t="inlineStr">
         <is>
           <t>If it's high</t>
@@ -23493,7 +23493,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Your bookings are real. Push volume upstream.</t>
+          <t>Your bookings are real. Push volume upstream. Over a single week this can read above 100% — a call booked on Friday gets shown on Monday, so inside a 7-day window the shows can outnumber the bookings. It is not a broken number. Judge show rate on the month or all-time column, never on one week.</t>
         </is>
       </c>
     </row>

--- a/docs/The_Called_Scoreboard.xlsx
+++ b/docs/The_Called_Scoreboard.xlsx
@@ -23185,10 +23185,10 @@
         </is>
       </c>
       <c r="C11" s="89" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="D11" s="89" t="n">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -23203,10 +23203,10 @@
         </is>
       </c>
       <c r="C12" s="89" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="D12" s="89" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -23221,10 +23221,10 @@
         </is>
       </c>
       <c r="C13" s="89" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="D13" s="89" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -23239,10 +23239,10 @@
         </is>
       </c>
       <c r="C14" s="89" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="D14" s="89" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -23257,10 +23257,10 @@
         </is>
       </c>
       <c r="C15" s="89" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D15" s="89" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1">

--- a/docs/The_Called_Scoreboard.xlsx
+++ b/docs/The_Called_Scoreboard.xlsx
@@ -20347,8 +20347,13 @@
       </c>
       <c r="G30" s="77" t="inlineStr">
         <is>
-          <t>Healthy
-floor</t>
+          <t>Red
+below</t>
+        </is>
+      </c>
+      <c r="H30" s="77" t="inlineStr">
+        <is>
+          <t>The bar</t>
         </is>
       </c>
     </row>
@@ -20382,6 +20387,10 @@
         <f>'Cheat Sheet'!$C$11</f>
         <v/>
       </c>
+      <c r="H31" s="78">
+        <f>'Cheat Sheet'!$D$11</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="75" t="inlineStr">
@@ -20413,6 +20422,10 @@
         <f>'Cheat Sheet'!$C$12</f>
         <v/>
       </c>
+      <c r="H32" s="78">
+        <f>'Cheat Sheet'!$D$12</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="75" t="inlineStr">
@@ -20444,6 +20457,10 @@
         <f>'Cheat Sheet'!$C$13</f>
         <v/>
       </c>
+      <c r="H33" s="78">
+        <f>'Cheat Sheet'!$D$13</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="75" t="inlineStr">
@@ -20475,6 +20492,10 @@
         <f>'Cheat Sheet'!$C$14</f>
         <v/>
       </c>
+      <c r="H34" s="78">
+        <f>'Cheat Sheet'!$D$14</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="75" t="inlineStr">
@@ -20504,6 +20525,10 @@
       </c>
       <c r="G35" s="78">
         <f>'Cheat Sheet'!$C$15</f>
+        <v/>
+      </c>
+      <c r="H35" s="78">
+        <f>'Cheat Sheet'!$D$15</f>
         <v/>
       </c>
     </row>
@@ -20816,17 +20841,20 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:F35">
     <cfRule type="expression" priority="3" dxfId="0">
-      <formula>AND(B31&lt;&gt;"",B31&gt;=$G31)</formula>
+      <formula>AND(B31&lt;&gt;"",B31&gt;=$H31)</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="2">
       <formula>AND(B31&lt;&gt;"",B31&lt;$G31)</formula>
     </cfRule>
+    <cfRule type="expression" priority="5" dxfId="4">
+      <formula>AND(B31&lt;&gt;"",B31&gt;=$G31,B31&lt;$H31)</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B41:F44">
-    <cfRule type="expression" priority="5" dxfId="0">
+    <cfRule type="expression" priority="6" dxfId="0">
       <formula>AND(B41&lt;&gt;"",B41&gt;=$G41)</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" dxfId="2">
+    <cfRule type="expression" priority="7" dxfId="2">
       <formula>AND(B41&lt;&gt;"",B41&lt;$G41)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23162,14 +23190,14 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Healthy
-floor</t>
+          <t>Red
+below</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Healthy
-ceiling</t>
+          <t>The bar
+(green at/above)</t>
         </is>
       </c>
     </row>
@@ -23185,10 +23213,10 @@
         </is>
       </c>
       <c r="C11" s="89" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D11" s="89" t="n">
         <v>0.5</v>
-      </c>
-      <c r="D11" s="89" t="n">
-        <v>0.8</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -23203,10 +23231,10 @@
         </is>
       </c>
       <c r="C12" s="89" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D12" s="89" t="n">
         <v>0.25</v>
-      </c>
-      <c r="D12" s="89" t="n">
-        <v>0.4</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -23221,10 +23249,10 @@
         </is>
       </c>
       <c r="C13" s="89" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D13" s="89" t="n">
         <v>0.6</v>
-      </c>
-      <c r="D13" s="89" t="n">
-        <v>0.8</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -23239,10 +23267,10 @@
         </is>
       </c>
       <c r="C14" s="89" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D14" s="89" t="n">
         <v>0.7</v>
-      </c>
-      <c r="D14" s="89" t="n">
-        <v>0.9</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -23257,16 +23285,16 @@
         </is>
       </c>
       <c r="C15" s="89" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D15" s="89" t="n">
         <v>0.4</v>
-      </c>
-      <c r="D15" s="89" t="n">
-        <v>0.7</v>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="B16" s="90" t="inlineStr">
         <is>
-          <t>These are The Called's working numbers, not gospel — they are cream cells because they are yours to change. The KPI Dashboard colours your rates against the FLOOR column: edit a floor here and the dashboard re-grades itself. Once you have enough client history, replace these with what you actually see.</t>
+          <t>Two numbers, two meanings. THE BAR is what we push you towards — hit it and the dashboard goes green. RED BELOW is the line where something is actually broken. In between you are amber: working, not there yet. That is most people most of the time, and it is not a failure. Both are cream cells because your coach can tune them to you, and the KPI Dashboard re-grades itself the moment they change.</t>
         </is>
       </c>
     </row>
